--- a/docs/PRAP_NewApp_Development_Plan_v1.2.xlsx
+++ b/docs/PRAP_NewApp_Development_Plan_v1.2.xlsx
@@ -11878,12 +11878,12 @@
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Desktop-specific UI design: eight screens, built as a clickable prototype rather than described.</t>
+          <t>Desktop-specific UI design: eight screens, built as a clickable prototype; then the real application wrapped in the desktop chrome and loaded with the 62-project dummy dataset, so the figures and charts can be reviewed as they will be.</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>app/PM_APP_Prototype_v0.1.html</t>
+          <t>app/PM_APP_Prototype_v0.2.html</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
